--- a/output/요금제현황_20260527.xlsx
+++ b/output/요금제현황_20260527.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10317" uniqueCount="1296">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10032" uniqueCount="1275">
   <si>
     <t>회사명</t>
   </si>
@@ -3508,9 +3508,6 @@
     <t>집/이동전화 200분</t>
   </si>
   <si>
-    <t>비노출</t>
-  </si>
-  <si>
     <t>5G 통화 충분 10GB</t>
   </si>
   <si>
@@ -3827,66 +3824,6 @@
   </si>
   <si>
     <t>충분 20GB</t>
-  </si>
-  <si>
-    <t>pl208r986</t>
-  </si>
-  <si>
-    <t>NEW</t>
-  </si>
-  <si>
-    <t>pl209o190</t>
-  </si>
-  <si>
-    <t>pl209o191</t>
-  </si>
-  <si>
-    <t>pl211r746</t>
-  </si>
-  <si>
-    <t>pl2192921</t>
-  </si>
-  <si>
-    <t>pl2192922</t>
-  </si>
-  <si>
-    <t>pl21cm686</t>
-  </si>
-  <si>
-    <t>pl229s135</t>
-  </si>
-  <si>
-    <t>pl22bs573</t>
-  </si>
-  <si>
-    <t>pl22bs575</t>
-  </si>
-  <si>
-    <t>pl22bs577</t>
-  </si>
-  <si>
-    <t>pl234d618</t>
-  </si>
-  <si>
-    <t>pl235q985</t>
-  </si>
-  <si>
-    <t>pl237i261</t>
-  </si>
-  <si>
-    <t>pl246o441</t>
-  </si>
-  <si>
-    <t>pl259C345</t>
-  </si>
-  <si>
-    <t>pl261t206</t>
-  </si>
-  <si>
-    <t>pl261t208</t>
-  </si>
-  <si>
-    <t>pl261t209</t>
   </si>
   <si>
     <t>SOS 스쿨 2GB+</t>
@@ -3908,7 +3845,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.##"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -3924,23 +3861,8 @@
     <font>
       <sz val="10"/>
     </font>
-    <font>
-      <i/>
-      <color rgb="FF999999"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <i/>
-      <color rgb="FF808080"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="FF0070C0"/>
-      <sz val="10"/>
-    </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3955,11 +3877,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE8F0FE"/>
       </patternFill>
     </fill>
   </fills>
@@ -3984,7 +3901,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4018,45 +3935,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4397,7 +4275,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M1092"/>
+  <dimension ref="A1:M1073"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -37273,7 +37151,7 @@
         <v>36</v>
       </c>
       <c r="G802" s="3">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="H802" s="2" t="s">
         <v>40</v>
@@ -44470,44 +44348,44 @@
       </c>
     </row>
     <row r="978" ht="16" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A978" s="12" t="s">
+      <c r="A978" s="2" t="s">
         <v>1151</v>
       </c>
-      <c r="B978" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="C978" s="12" t="s">
+      <c r="B978" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C978" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D978" s="12" t="s">
+      <c r="D978" s="2" t="s">
         <v>1163</v>
       </c>
-      <c r="E978" s="12" t="s">
+      <c r="E978" s="2" t="s">
         <v>1164</v>
       </c>
-      <c r="F978" s="12" t="s">
+      <c r="F978" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="G978" s="13">
+      <c r="G978" s="3">
         <v>10</v>
       </c>
-      <c r="H978" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="I978" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="J978" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="K978" s="15">
+      <c r="H978" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I978" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="J978" s="4">
+        <v>17900</v>
+      </c>
+      <c r="K978" s="4">
         <v>10900</v>
       </c>
-      <c r="L978" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="M978" s="16" t="s">
-        <v>1165</v>
+      <c r="L978" s="4">
+        <v>10900</v>
+      </c>
+      <c r="M978" s="5" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="979" ht="16" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -44521,10 +44399,10 @@
         <v>15</v>
       </c>
       <c r="D979" s="6" t="s">
+        <v>1165</v>
+      </c>
+      <c r="E979" s="6" t="s">
         <v>1166</v>
-      </c>
-      <c r="E979" s="6" t="s">
-        <v>1167</v>
       </c>
       <c r="F979" s="6" t="s">
         <v>36</v>
@@ -44562,10 +44440,10 @@
         <v>15</v>
       </c>
       <c r="D980" s="2" t="s">
+        <v>1167</v>
+      </c>
+      <c r="E980" s="2" t="s">
         <v>1168</v>
-      </c>
-      <c r="E980" s="2" t="s">
-        <v>1169</v>
       </c>
       <c r="F980" s="2" t="s">
         <v>36</v>
@@ -44603,10 +44481,10 @@
         <v>15</v>
       </c>
       <c r="D981" s="6" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
       <c r="E981" s="6" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="F981" s="6" t="s">
         <v>36</v>
@@ -44634,85 +44512,85 @@
       </c>
     </row>
     <row r="982" ht="16" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A982" s="12" t="s">
+      <c r="A982" s="2" t="s">
         <v>1151</v>
       </c>
-      <c r="B982" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="C982" s="12" t="s">
+      <c r="B982" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C982" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D982" s="12" t="s">
+      <c r="D982" s="2" t="s">
+        <v>1170</v>
+      </c>
+      <c r="E982" s="2" t="s">
+        <v>1166</v>
+      </c>
+      <c r="F982" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="G982" s="3">
+        <v>3</v>
+      </c>
+      <c r="H982" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I982" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="J982" s="4">
+        <v>14900</v>
+      </c>
+      <c r="K982" s="4">
+        <v>8900</v>
+      </c>
+      <c r="L982" s="4">
+        <v>8900</v>
+      </c>
+      <c r="M982" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="983" ht="16" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A983" s="6" t="s">
+        <v>1151</v>
+      </c>
+      <c r="B983" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C983" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D983" s="6" t="s">
         <v>1171</v>
       </c>
-      <c r="E982" s="12" t="s">
-        <v>1167</v>
-      </c>
-      <c r="F982" s="12" t="s">
-        <v>36</v>
-      </c>
-      <c r="G982" s="13">
-        <v>3</v>
-      </c>
-      <c r="H982" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="I982" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="J982" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="K982" s="15">
-        <v>8900</v>
-      </c>
-      <c r="L982" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="M982" s="16" t="s">
-        <v>1165</v>
-      </c>
-    </row>
-    <row r="983" ht="16" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A983" s="17" t="s">
-        <v>1151</v>
-      </c>
-      <c r="B983" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="C983" s="17" t="s">
-        <v>15</v>
-      </c>
-      <c r="D983" s="17" t="s">
-        <v>1172</v>
-      </c>
-      <c r="E983" s="17" t="s">
-        <v>1167</v>
-      </c>
-      <c r="F983" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="G983" s="18">
+      <c r="E983" s="6" t="s">
+        <v>1166</v>
+      </c>
+      <c r="F983" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="G983" s="7">
         <v>6</v>
       </c>
-      <c r="H983" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="I983" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="J983" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="K983" s="20">
+      <c r="H983" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="I983" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="J983" s="8">
+        <v>17900</v>
+      </c>
+      <c r="K983" s="8">
         <v>11900</v>
       </c>
-      <c r="L983" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="M983" s="21" t="s">
-        <v>1165</v>
+      <c r="L983" s="8">
+        <v>11900</v>
+      </c>
+      <c r="M983" s="9" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="984" ht="16" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -44726,10 +44604,10 @@
         <v>15</v>
       </c>
       <c r="D984" s="2" t="s">
+        <v>1172</v>
+      </c>
+      <c r="E984" s="2" t="s">
         <v>1173</v>
-      </c>
-      <c r="E984" s="2" t="s">
-        <v>1174</v>
       </c>
       <c r="F984" s="2" t="s">
         <v>79</v>
@@ -44767,10 +44645,10 @@
         <v>15</v>
       </c>
       <c r="D985" s="6" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="E985" s="6" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="F985" s="6" t="s">
         <v>79</v>
@@ -44808,10 +44686,10 @@
         <v>15</v>
       </c>
       <c r="D986" s="2" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="E986" s="2" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="F986" s="2" t="s">
         <v>79</v>
@@ -44849,10 +44727,10 @@
         <v>15</v>
       </c>
       <c r="D987" s="6" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="E987" s="6" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="F987" s="6" t="s">
         <v>79</v>
@@ -44890,10 +44768,10 @@
         <v>15</v>
       </c>
       <c r="D988" s="2" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="E988" s="2" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="F988" s="2" t="s">
         <v>79</v>
@@ -44931,10 +44809,10 @@
         <v>15</v>
       </c>
       <c r="D989" s="6" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="E989" s="6" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="F989" s="6" t="s">
         <v>79</v>
@@ -44972,10 +44850,10 @@
         <v>15</v>
       </c>
       <c r="D990" s="2" t="s">
+        <v>1179</v>
+      </c>
+      <c r="E990" s="2" t="s">
         <v>1180</v>
-      </c>
-      <c r="E990" s="2" t="s">
-        <v>1181</v>
       </c>
       <c r="F990" s="2" t="s">
         <v>109</v>
@@ -45013,10 +44891,10 @@
         <v>15</v>
       </c>
       <c r="D991" s="6" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="E991" s="6" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="F991" s="6" t="s">
         <v>109</v>
@@ -45044,85 +44922,85 @@
       </c>
     </row>
     <row r="992" ht="16" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A992" s="12" t="s">
+      <c r="A992" s="2" t="s">
         <v>1151</v>
       </c>
-      <c r="B992" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="C992" s="12" t="s">
+      <c r="B992" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C992" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D992" s="12" t="s">
+      <c r="D992" s="2" t="s">
+        <v>1182</v>
+      </c>
+      <c r="E992" s="2" t="s">
+        <v>1173</v>
+      </c>
+      <c r="F992" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="G992" s="3">
+        <v>5</v>
+      </c>
+      <c r="H992" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="I992" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="J992" s="4">
+        <v>14300</v>
+      </c>
+      <c r="K992" s="4">
+        <v>14300</v>
+      </c>
+      <c r="L992" s="4">
+        <v>14300</v>
+      </c>
+      <c r="M992" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="993" ht="16" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A993" s="6" t="s">
+        <v>1151</v>
+      </c>
+      <c r="B993" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C993" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D993" s="6" t="s">
         <v>1183</v>
       </c>
-      <c r="E992" s="12" t="s">
-        <v>1174</v>
-      </c>
-      <c r="F992" s="12" t="s">
-        <v>79</v>
-      </c>
-      <c r="G992" s="13">
-        <v>5</v>
-      </c>
-      <c r="H992" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="I992" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="J992" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="K992" s="15">
-        <v>14300</v>
-      </c>
-      <c r="L992" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="M992" s="16" t="s">
-        <v>1165</v>
-      </c>
-    </row>
-    <row r="993" ht="16" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A993" s="17" t="s">
-        <v>1151</v>
-      </c>
-      <c r="B993" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="C993" s="17" t="s">
-        <v>15</v>
-      </c>
-      <c r="D993" s="17" t="s">
+      <c r="E993" s="6" t="s">
+        <v>1153</v>
+      </c>
+      <c r="F993" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="G993" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="H993" s="6" t="s">
         <v>1184</v>
       </c>
-      <c r="E993" s="17" t="s">
-        <v>1153</v>
-      </c>
-      <c r="F993" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="G993" s="18">
-        <v>1.5</v>
-      </c>
-      <c r="H993" s="17" t="s">
-        <v>1185</v>
-      </c>
-      <c r="I993" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="J993" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="K993" s="20">
+      <c r="I993" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="J993" s="8">
+        <v>9900</v>
+      </c>
+      <c r="K993" s="8">
         <v>6900</v>
       </c>
-      <c r="L993" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="M993" s="21" t="s">
-        <v>1165</v>
+      <c r="L993" s="8">
+        <v>6900</v>
+      </c>
+      <c r="M993" s="9" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="994" ht="16" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -45136,7 +45014,7 @@
         <v>15</v>
       </c>
       <c r="D994" s="2" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="E994" s="2" t="s">
         <v>1153</v>
@@ -45177,7 +45055,7 @@
         <v>15</v>
       </c>
       <c r="D995" s="6" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
       <c r="E995" s="6" t="s">
         <v>1153</v>
@@ -45218,7 +45096,7 @@
         <v>15</v>
       </c>
       <c r="D996" s="2" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="E996" s="2" t="s">
         <v>1153</v>
@@ -45259,7 +45137,7 @@
         <v>15</v>
       </c>
       <c r="D997" s="6" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="E997" s="6" t="s">
         <v>1153</v>
@@ -45300,7 +45178,7 @@
         <v>15</v>
       </c>
       <c r="D998" s="2" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
       <c r="E998" s="2" t="s">
         <v>1153</v>
@@ -45341,7 +45219,7 @@
         <v>15</v>
       </c>
       <c r="D999" s="6" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="E999" s="6" t="s">
         <v>1153</v>
@@ -45382,7 +45260,7 @@
         <v>15</v>
       </c>
       <c r="D1000" s="2" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="E1000" s="2" t="s">
         <v>1153</v>
@@ -45423,7 +45301,7 @@
         <v>15</v>
       </c>
       <c r="D1001" s="6" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="E1001" s="6" t="s">
         <v>1153</v>
@@ -45464,7 +45342,7 @@
         <v>15</v>
       </c>
       <c r="D1002" s="2" t="s">
-        <v>1194</v>
+        <v>1193</v>
       </c>
       <c r="E1002" s="2" t="s">
         <v>1153</v>
@@ -45476,7 +45354,7 @@
         <v>2.5</v>
       </c>
       <c r="H1002" s="2" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="I1002" s="2" t="s">
         <v>19</v>
@@ -45505,7 +45383,7 @@
         <v>15</v>
       </c>
       <c r="D1003" s="6" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="E1003" s="6" t="s">
         <v>1153</v>
@@ -45517,7 +45395,7 @@
         <v>4.5</v>
       </c>
       <c r="H1003" s="6" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="I1003" s="6" t="s">
         <v>19</v>
@@ -45546,7 +45424,7 @@
         <v>15</v>
       </c>
       <c r="D1004" s="2" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="E1004" s="2" t="s">
         <v>1153</v>
@@ -45587,10 +45465,10 @@
         <v>15</v>
       </c>
       <c r="D1005" s="6" t="s">
+        <v>1196</v>
+      </c>
+      <c r="E1005" s="6" t="s">
         <v>1197</v>
-      </c>
-      <c r="E1005" s="6" t="s">
-        <v>1198</v>
       </c>
       <c r="F1005" s="6" t="s">
         <v>498</v>
@@ -45618,208 +45496,208 @@
       </c>
     </row>
     <row r="1006" ht="16" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1006" s="12" t="s">
+      <c r="A1006" s="2" t="s">
         <v>1151</v>
       </c>
-      <c r="B1006" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="C1006" s="12" t="s">
+      <c r="B1006" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1006" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D1006" s="12" t="s">
+      <c r="D1006" s="2" t="s">
+        <v>1198</v>
+      </c>
+      <c r="E1006" s="2" t="s">
         <v>1199</v>
       </c>
-      <c r="E1006" s="12" t="s">
+      <c r="F1006" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="G1006" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="H1006" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I1006" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1006" s="4">
+        <v>35200</v>
+      </c>
+      <c r="K1006" s="4">
+        <v>6600</v>
+      </c>
+      <c r="L1006" s="4">
+        <v>6600</v>
+      </c>
+      <c r="M1006" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1007" ht="16" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1007" s="6" t="s">
+        <v>1151</v>
+      </c>
+      <c r="B1007" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1007" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1007" s="6" t="s">
         <v>1200</v>
       </c>
-      <c r="F1006" s="12" t="s">
-        <v>36</v>
-      </c>
-      <c r="G1006" s="13">
-        <v>1.5</v>
-      </c>
-      <c r="H1006" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="I1006" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="J1006" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="K1006" s="15">
-        <v>6600</v>
-      </c>
-      <c r="L1006" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="M1006" s="16" t="s">
-        <v>1165</v>
-      </c>
-    </row>
-    <row r="1007" ht="16" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1007" s="17" t="s">
+      <c r="E1007" s="6" t="s">
+        <v>1201</v>
+      </c>
+      <c r="F1007" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="G1007" s="7">
+        <v>15</v>
+      </c>
+      <c r="H1007" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="I1007" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1007" s="8">
+        <v>19500</v>
+      </c>
+      <c r="K1007" s="8">
+        <v>16900</v>
+      </c>
+      <c r="L1007" s="8">
+        <v>16900</v>
+      </c>
+      <c r="M1007" s="9" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1008" ht="16" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1008" s="2" t="s">
         <v>1151</v>
       </c>
-      <c r="B1007" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="C1007" s="17" t="s">
+      <c r="B1008" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1008" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D1007" s="17" t="s">
-        <v>1201</v>
-      </c>
-      <c r="E1007" s="17" t="s">
+      <c r="D1008" s="2" t="s">
         <v>1202</v>
       </c>
-      <c r="F1007" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="G1007" s="18">
+      <c r="E1008" s="2" t="s">
+        <v>1203</v>
+      </c>
+      <c r="F1008" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="G1008" s="3">
+        <v>2.5</v>
+      </c>
+      <c r="H1008" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I1008" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1008" s="4">
+        <v>42900</v>
+      </c>
+      <c r="K1008" s="4">
+        <v>7700</v>
+      </c>
+      <c r="L1008" s="4">
+        <v>7700</v>
+      </c>
+      <c r="M1008" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1009" ht="16" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1009" s="6" t="s">
+        <v>1151</v>
+      </c>
+      <c r="B1009" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1009" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="H1007" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="I1007" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="J1007" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="K1007" s="20">
-        <v>16900</v>
-      </c>
-      <c r="L1007" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="M1007" s="21" t="s">
-        <v>1165</v>
-      </c>
-    </row>
-    <row r="1008" ht="16" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1008" s="12" t="s">
+      <c r="D1009" s="6" t="s">
+        <v>1204</v>
+      </c>
+      <c r="E1009" s="6" t="s">
+        <v>1205</v>
+      </c>
+      <c r="F1009" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="G1009" s="7">
+        <v>4.5</v>
+      </c>
+      <c r="H1009" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="I1009" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1009" s="8">
+        <v>42900</v>
+      </c>
+      <c r="K1009" s="8">
+        <v>8850</v>
+      </c>
+      <c r="L1009" s="8">
+        <v>8850</v>
+      </c>
+      <c r="M1009" s="9" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1010" ht="16" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1010" s="2" t="s">
         <v>1151</v>
       </c>
-      <c r="B1008" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="C1008" s="12" t="s">
+      <c r="B1010" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1010" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D1008" s="12" t="s">
-        <v>1203</v>
-      </c>
-      <c r="E1008" s="12" t="s">
-        <v>1204</v>
-      </c>
-      <c r="F1008" s="12" t="s">
-        <v>36</v>
-      </c>
-      <c r="G1008" s="13">
-        <v>2.5</v>
-      </c>
-      <c r="H1008" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="I1008" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="J1008" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="K1008" s="15">
-        <v>7700</v>
-      </c>
-      <c r="L1008" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="M1008" s="16" t="s">
-        <v>1165</v>
-      </c>
-    </row>
-    <row r="1009" ht="16" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1009" s="17" t="s">
-        <v>1151</v>
-      </c>
-      <c r="B1009" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="C1009" s="17" t="s">
-        <v>15</v>
-      </c>
-      <c r="D1009" s="17" t="s">
-        <v>1205</v>
-      </c>
-      <c r="E1009" s="17" t="s">
+      <c r="D1010" s="2" t="s">
         <v>1206</v>
       </c>
-      <c r="F1009" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="G1009" s="18">
-        <v>4.5</v>
-      </c>
-      <c r="H1009" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="I1009" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="J1009" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="K1009" s="20">
-        <v>8850</v>
-      </c>
-      <c r="L1009" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="M1009" s="21" t="s">
-        <v>1165</v>
-      </c>
-    </row>
-    <row r="1010" ht="16" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1010" s="12" t="s">
-        <v>1151</v>
-      </c>
-      <c r="B1010" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="C1010" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="D1010" s="12" t="s">
+      <c r="E1010" s="2" t="s">
         <v>1207</v>
       </c>
-      <c r="E1010" s="12" t="s">
-        <v>1208</v>
-      </c>
-      <c r="F1010" s="12" t="s">
-        <v>36</v>
-      </c>
-      <c r="G1010" s="13">
+      <c r="F1010" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="G1010" s="3">
         <v>6.5</v>
       </c>
-      <c r="H1010" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="I1010" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="J1010" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="K1010" s="15">
+      <c r="H1010" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I1010" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1010" s="4">
+        <v>11900</v>
+      </c>
+      <c r="K1010" s="4">
         <v>10900</v>
       </c>
-      <c r="L1010" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="M1010" s="16" t="s">
-        <v>1165</v>
+      <c r="L1010" s="4">
+        <v>10900</v>
+      </c>
+      <c r="M1010" s="5" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="1011" ht="16" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -45833,7 +45711,7 @@
         <v>240</v>
       </c>
       <c r="D1011" s="6" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="E1011" s="6" t="s">
         <v>1153</v>
@@ -45845,7 +45723,7 @@
         <v>2</v>
       </c>
       <c r="H1011" s="6" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="I1011" s="6" t="s">
         <v>19</v>
@@ -45874,7 +45752,7 @@
         <v>240</v>
       </c>
       <c r="D1012" s="2" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="E1012" s="2" t="s">
         <v>1153</v>
@@ -45915,10 +45793,10 @@
         <v>240</v>
       </c>
       <c r="D1013" s="6" t="s">
-        <v>1211</v>
+        <v>1210</v>
       </c>
       <c r="E1013" s="6" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="F1013" s="6" t="s">
         <v>109</v>
@@ -45946,85 +45824,85 @@
       </c>
     </row>
     <row r="1014" ht="16" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1014" s="12" t="s">
+      <c r="A1014" s="2" t="s">
         <v>1151</v>
       </c>
-      <c r="B1014" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="C1014" s="12" t="s">
-        <v>240</v>
-      </c>
-      <c r="D1014" s="12" t="s">
+      <c r="B1014" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1014" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="D1014" s="2" t="s">
+        <v>1211</v>
+      </c>
+      <c r="E1014" s="2" t="s">
+        <v>1153</v>
+      </c>
+      <c r="F1014" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="G1014" s="3">
+        <v>8</v>
+      </c>
+      <c r="H1014" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="I1014" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1014" s="4">
+        <v>14900</v>
+      </c>
+      <c r="K1014" s="4">
+        <v>13900</v>
+      </c>
+      <c r="L1014" s="4">
+        <v>13900</v>
+      </c>
+      <c r="M1014" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1015" ht="16" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1015" s="6" t="s">
+        <v>1151</v>
+      </c>
+      <c r="B1015" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1015" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="D1015" s="6" t="s">
         <v>1212</v>
       </c>
-      <c r="E1014" s="12" t="s">
-        <v>1153</v>
-      </c>
-      <c r="F1014" s="12" t="s">
-        <v>36</v>
-      </c>
-      <c r="G1014" s="13">
-        <v>8</v>
-      </c>
-      <c r="H1014" s="12" t="s">
+      <c r="E1015" s="6" t="s">
+        <v>1173</v>
+      </c>
+      <c r="F1015" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="G1015" s="7">
+        <v>2.2</v>
+      </c>
+      <c r="H1015" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="I1014" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="J1014" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="K1014" s="15">
-        <v>13900</v>
-      </c>
-      <c r="L1014" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="M1014" s="16" t="s">
-        <v>1165</v>
-      </c>
-    </row>
-    <row r="1015" ht="16" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1015" s="17" t="s">
-        <v>1151</v>
-      </c>
-      <c r="B1015" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="C1015" s="17" t="s">
-        <v>240</v>
-      </c>
-      <c r="D1015" s="17" t="s">
-        <v>1213</v>
-      </c>
-      <c r="E1015" s="17" t="s">
-        <v>1174</v>
-      </c>
-      <c r="F1015" s="17" t="s">
-        <v>79</v>
-      </c>
-      <c r="G1015" s="18">
-        <v>2.2</v>
-      </c>
-      <c r="H1015" s="17" t="s">
-        <v>40</v>
-      </c>
-      <c r="I1015" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="J1015" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="K1015" s="20">
+      <c r="I1015" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1015" s="8">
         <v>11700</v>
       </c>
-      <c r="L1015" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="M1015" s="21" t="s">
-        <v>1165</v>
+      <c r="K1015" s="8">
+        <v>11700</v>
+      </c>
+      <c r="L1015" s="8">
+        <v>11700</v>
+      </c>
+      <c r="M1015" s="9" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="1016" ht="16" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -46038,7 +45916,7 @@
         <v>240</v>
       </c>
       <c r="D1016" s="2" t="s">
-        <v>1214</v>
+        <v>1213</v>
       </c>
       <c r="E1016" s="2" t="s">
         <v>1153</v>
@@ -46079,7 +45957,7 @@
         <v>240</v>
       </c>
       <c r="D1017" s="6" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="E1017" s="6" t="s">
         <v>1153</v>
@@ -46120,7 +45998,7 @@
         <v>240</v>
       </c>
       <c r="D1018" s="2" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="E1018" s="2" t="s">
         <v>1153</v>
@@ -46161,7 +46039,7 @@
         <v>240</v>
       </c>
       <c r="D1019" s="6" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="E1019" s="6" t="s">
         <v>1153</v>
@@ -46202,7 +46080,7 @@
         <v>240</v>
       </c>
       <c r="D1020" s="2" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="E1020" s="2" t="s">
         <v>1153</v>
@@ -46243,7 +46121,7 @@
         <v>240</v>
       </c>
       <c r="D1021" s="6" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="E1021" s="6" t="s">
         <v>1153</v>
@@ -46284,7 +46162,7 @@
         <v>240</v>
       </c>
       <c r="D1022" s="2" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="E1022" s="2" t="s">
         <v>1153</v>
@@ -46325,7 +46203,7 @@
         <v>240</v>
       </c>
       <c r="D1023" s="6" t="s">
-        <v>1221</v>
+        <v>1220</v>
       </c>
       <c r="E1023" s="6" t="s">
         <v>1153</v>
@@ -46366,7 +46244,7 @@
         <v>240</v>
       </c>
       <c r="D1024" s="2" t="s">
-        <v>1222</v>
+        <v>1221</v>
       </c>
       <c r="E1024" s="2" t="s">
         <v>1153</v>
@@ -46378,7 +46256,7 @@
         <v>10</v>
       </c>
       <c r="H1024" s="2" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="I1024" s="2" t="s">
         <v>19</v>
@@ -46407,7 +46285,7 @@
         <v>240</v>
       </c>
       <c r="D1025" s="6" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="E1025" s="6" t="s">
         <v>1153</v>
@@ -46448,7 +46326,7 @@
         <v>240</v>
       </c>
       <c r="D1026" s="2" t="s">
-        <v>1224</v>
+        <v>1223</v>
       </c>
       <c r="E1026" s="2" t="s">
         <v>1153</v>
@@ -46489,7 +46367,7 @@
         <v>240</v>
       </c>
       <c r="D1027" s="6" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="E1027" s="6" t="s">
         <v>1153</v>
@@ -46530,7 +46408,7 @@
         <v>240</v>
       </c>
       <c r="D1028" s="2" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
       <c r="E1028" s="2" t="s">
         <v>1153</v>
@@ -46571,7 +46449,7 @@
         <v>240</v>
       </c>
       <c r="D1029" s="6" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="E1029" s="6" t="s">
         <v>1153</v>
@@ -46612,7 +46490,7 @@
         <v>240</v>
       </c>
       <c r="D1030" s="2" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
       <c r="E1030" s="2" t="s">
         <v>1153</v>
@@ -46653,7 +46531,7 @@
         <v>240</v>
       </c>
       <c r="D1031" s="6" t="s">
-        <v>1229</v>
+        <v>1228</v>
       </c>
       <c r="E1031" s="6" t="s">
         <v>1153</v>
@@ -46694,7 +46572,7 @@
         <v>240</v>
       </c>
       <c r="D1032" s="2" t="s">
-        <v>1230</v>
+        <v>1229</v>
       </c>
       <c r="E1032" s="2" t="s">
         <v>1153</v>
@@ -46735,7 +46613,7 @@
         <v>240</v>
       </c>
       <c r="D1033" s="6" t="s">
-        <v>1231</v>
+        <v>1230</v>
       </c>
       <c r="E1033" s="6" t="s">
         <v>1153</v>
@@ -46776,7 +46654,7 @@
         <v>240</v>
       </c>
       <c r="D1034" s="2" t="s">
-        <v>1232</v>
+        <v>1231</v>
       </c>
       <c r="E1034" s="2" t="s">
         <v>1153</v>
@@ -46817,7 +46695,7 @@
         <v>240</v>
       </c>
       <c r="D1035" s="6" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
       <c r="E1035" s="6" t="s">
         <v>1153</v>
@@ -46858,7 +46736,7 @@
         <v>240</v>
       </c>
       <c r="D1036" s="2" t="s">
-        <v>1234</v>
+        <v>1233</v>
       </c>
       <c r="E1036" s="2" t="s">
         <v>1153</v>
@@ -46899,7 +46777,7 @@
         <v>240</v>
       </c>
       <c r="D1037" s="6" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
       <c r="E1037" s="6" t="s">
         <v>1153</v>
@@ -46940,7 +46818,7 @@
         <v>240</v>
       </c>
       <c r="D1038" s="2" t="s">
-        <v>1236</v>
+        <v>1235</v>
       </c>
       <c r="E1038" s="2" t="s">
         <v>1153</v>
@@ -46981,7 +46859,7 @@
         <v>240</v>
       </c>
       <c r="D1039" s="6" t="s">
-        <v>1237</v>
+        <v>1236</v>
       </c>
       <c r="E1039" s="6" t="s">
         <v>1153</v>
@@ -47022,7 +46900,7 @@
         <v>240</v>
       </c>
       <c r="D1040" s="2" t="s">
-        <v>1238</v>
+        <v>1237</v>
       </c>
       <c r="E1040" s="2" t="s">
         <v>1153</v>
@@ -47063,7 +46941,7 @@
         <v>240</v>
       </c>
       <c r="D1041" s="6" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="E1041" s="6" t="s">
         <v>1153</v>
@@ -47104,7 +46982,7 @@
         <v>240</v>
       </c>
       <c r="D1042" s="2" t="s">
-        <v>1240</v>
+        <v>1239</v>
       </c>
       <c r="E1042" s="2" t="s">
         <v>1153</v>
@@ -47145,7 +47023,7 @@
         <v>240</v>
       </c>
       <c r="D1043" s="6" t="s">
-        <v>1241</v>
+        <v>1240</v>
       </c>
       <c r="E1043" s="6" t="s">
         <v>1153</v>
@@ -47186,7 +47064,7 @@
         <v>240</v>
       </c>
       <c r="D1044" s="2" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
       <c r="E1044" s="2" t="s">
         <v>1153</v>
@@ -47227,7 +47105,7 @@
         <v>240</v>
       </c>
       <c r="D1045" s="6" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
       <c r="E1045" s="6" t="s">
         <v>1153</v>
@@ -47258,44 +47136,44 @@
       </c>
     </row>
     <row r="1046" ht="16" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1046" s="12" t="s">
+      <c r="A1046" s="2" t="s">
         <v>1151</v>
       </c>
-      <c r="B1046" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="C1046" s="12" t="s">
-        <v>240</v>
-      </c>
-      <c r="D1046" s="12" t="s">
-        <v>1244</v>
-      </c>
-      <c r="E1046" s="12" t="s">
+      <c r="B1046" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1046" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="D1046" s="2" t="s">
+        <v>1243</v>
+      </c>
+      <c r="E1046" s="2" t="s">
         <v>1153</v>
       </c>
-      <c r="F1046" s="12" t="s">
-        <v>36</v>
-      </c>
-      <c r="G1046" s="13">
+      <c r="F1046" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="G1046" s="3">
         <v>6</v>
       </c>
-      <c r="H1046" s="12" t="s">
-        <v>1185</v>
-      </c>
-      <c r="I1046" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="J1046" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="K1046" s="15">
+      <c r="H1046" s="2" t="s">
+        <v>1184</v>
+      </c>
+      <c r="I1046" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1046" s="4">
         <v>14900</v>
       </c>
-      <c r="L1046" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="M1046" s="16" t="s">
-        <v>1165</v>
+      <c r="K1046" s="4">
+        <v>14900</v>
+      </c>
+      <c r="L1046" s="4">
+        <v>14900</v>
+      </c>
+      <c r="M1046" s="5" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="1047" ht="16" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -47309,7 +47187,7 @@
         <v>240</v>
       </c>
       <c r="D1047" s="6" t="s">
-        <v>1245</v>
+        <v>1244</v>
       </c>
       <c r="E1047" s="6" t="s">
         <v>1153</v>
@@ -47340,85 +47218,85 @@
       </c>
     </row>
     <row r="1048" ht="16" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1048" s="12" t="s">
+      <c r="A1048" s="2" t="s">
         <v>1151</v>
       </c>
-      <c r="B1048" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="C1048" s="12" t="s">
-        <v>240</v>
-      </c>
-      <c r="D1048" s="12" t="s">
+      <c r="B1048" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1048" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="D1048" s="2" t="s">
+        <v>1245</v>
+      </c>
+      <c r="E1048" s="2" t="s">
+        <v>1153</v>
+      </c>
+      <c r="F1048" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="G1048" s="3">
+        <v>7</v>
+      </c>
+      <c r="H1048" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="I1048" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1048" s="4">
+        <v>22000</v>
+      </c>
+      <c r="K1048" s="4">
+        <v>16200</v>
+      </c>
+      <c r="L1048" s="4">
+        <v>16200</v>
+      </c>
+      <c r="M1048" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1049" ht="16" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1049" s="6" t="s">
+        <v>1151</v>
+      </c>
+      <c r="B1049" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1049" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="D1049" s="6" t="s">
         <v>1246</v>
       </c>
-      <c r="E1048" s="12" t="s">
+      <c r="E1049" s="6" t="s">
         <v>1153</v>
       </c>
-      <c r="F1048" s="12" t="s">
-        <v>36</v>
-      </c>
-      <c r="G1048" s="13">
+      <c r="F1049" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="G1049" s="7">
         <v>7</v>
       </c>
-      <c r="H1048" s="12" t="s">
+      <c r="H1049" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="I1048" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="J1048" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="K1048" s="15">
-        <v>16200</v>
-      </c>
-      <c r="L1048" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="M1048" s="16" t="s">
-        <v>1165</v>
-      </c>
-    </row>
-    <row r="1049" ht="16" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1049" s="17" t="s">
-        <v>1151</v>
-      </c>
-      <c r="B1049" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="C1049" s="17" t="s">
-        <v>240</v>
-      </c>
-      <c r="D1049" s="17" t="s">
-        <v>1247</v>
-      </c>
-      <c r="E1049" s="17" t="s">
-        <v>1153</v>
-      </c>
-      <c r="F1049" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="G1049" s="18">
-        <v>7</v>
-      </c>
-      <c r="H1049" s="17" t="s">
-        <v>40</v>
-      </c>
-      <c r="I1049" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="J1049" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="K1049" s="20">
+      <c r="I1049" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1049" s="8">
+        <v>22000</v>
+      </c>
+      <c r="K1049" s="8">
         <v>16300</v>
       </c>
-      <c r="L1049" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="M1049" s="21" t="s">
-        <v>1165</v>
+      <c r="L1049" s="8">
+        <v>16300</v>
+      </c>
+      <c r="M1049" s="9" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="1050" ht="16" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -47432,7 +47310,7 @@
         <v>240</v>
       </c>
       <c r="D1050" s="2" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="E1050" s="2" t="s">
         <v>1153</v>
@@ -47473,7 +47351,7 @@
         <v>240</v>
       </c>
       <c r="D1051" s="6" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="E1051" s="6" t="s">
         <v>1153</v>
@@ -47504,44 +47382,44 @@
       </c>
     </row>
     <row r="1052" ht="16" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1052" s="12" t="s">
+      <c r="A1052" s="2" t="s">
         <v>1151</v>
       </c>
-      <c r="B1052" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="C1052" s="12" t="s">
-        <v>240</v>
-      </c>
-      <c r="D1052" s="12" t="s">
-        <v>1250</v>
-      </c>
-      <c r="E1052" s="12" t="s">
+      <c r="B1052" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1052" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="D1052" s="2" t="s">
+        <v>1249</v>
+      </c>
+      <c r="E1052" s="2" t="s">
         <v>1153</v>
       </c>
-      <c r="F1052" s="12" t="s">
-        <v>36</v>
-      </c>
-      <c r="G1052" s="13">
+      <c r="F1052" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="G1052" s="3">
         <v>7</v>
       </c>
-      <c r="H1052" s="12" t="s">
+      <c r="H1052" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="I1052" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="J1052" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="K1052" s="15">
+      <c r="I1052" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1052" s="4">
+        <v>24200</v>
+      </c>
+      <c r="K1052" s="4">
         <v>16200</v>
       </c>
-      <c r="L1052" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="M1052" s="16" t="s">
-        <v>1165</v>
+      <c r="L1052" s="4">
+        <v>16200</v>
+      </c>
+      <c r="M1052" s="5" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="1053" ht="16" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -47555,7 +47433,7 @@
         <v>240</v>
       </c>
       <c r="D1053" s="6" t="s">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="E1053" s="6" t="s">
         <v>1153</v>
@@ -47596,7 +47474,7 @@
         <v>240</v>
       </c>
       <c r="D1054" s="2" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="E1054" s="2" t="s">
         <v>1153</v>
@@ -47637,10 +47515,10 @@
         <v>240</v>
       </c>
       <c r="D1055" s="6" t="s">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="E1055" s="6" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="F1055" s="6" t="s">
         <v>79</v>
@@ -47678,10 +47556,10 @@
         <v>240</v>
       </c>
       <c r="D1056" s="2" t="s">
+        <v>1253</v>
+      </c>
+      <c r="E1056" s="2" t="s">
         <v>1254</v>
-      </c>
-      <c r="E1056" s="2" t="s">
-        <v>1255</v>
       </c>
       <c r="F1056" s="2" t="s">
         <v>194</v>
@@ -47709,44 +47587,44 @@
       </c>
     </row>
     <row r="1057" ht="16" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1057" s="17" t="s">
+      <c r="A1057" s="6" t="s">
         <v>1151</v>
       </c>
-      <c r="B1057" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="C1057" s="17" t="s">
-        <v>240</v>
-      </c>
-      <c r="D1057" s="17" t="s">
-        <v>1256</v>
-      </c>
-      <c r="E1057" s="17" t="s">
+      <c r="B1057" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1057" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="D1057" s="6" t="s">
         <v>1255</v>
       </c>
-      <c r="F1057" s="17" t="s">
+      <c r="E1057" s="6" t="s">
+        <v>1254</v>
+      </c>
+      <c r="F1057" s="6" t="s">
         <v>194</v>
       </c>
-      <c r="G1057" s="18">
-        <v>20</v>
-      </c>
-      <c r="H1057" s="17" t="s">
+      <c r="G1057" s="7">
+        <v>20</v>
+      </c>
+      <c r="H1057" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="I1057" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="J1057" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="K1057" s="20">
+      <c r="I1057" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1057" s="8">
+        <v>24000</v>
+      </c>
+      <c r="K1057" s="8">
         <v>14100</v>
       </c>
-      <c r="L1057" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="M1057" s="21" t="s">
-        <v>1165</v>
+      <c r="L1057" s="8">
+        <v>14100</v>
+      </c>
+      <c r="M1057" s="9" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="1058" ht="16" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -47760,7 +47638,7 @@
         <v>240</v>
       </c>
       <c r="D1058" s="2" t="s">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="E1058" s="2" t="s">
         <v>1153</v>
@@ -47772,7 +47650,7 @@
         <v>2</v>
       </c>
       <c r="H1058" s="2" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="I1058" s="2" t="s">
         <v>19</v>
@@ -47801,7 +47679,7 @@
         <v>240</v>
       </c>
       <c r="D1059" s="6" t="s">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="E1059" s="6" t="s">
         <v>1153</v>
@@ -47813,7 +47691,7 @@
         <v>4</v>
       </c>
       <c r="H1059" s="6" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="I1059" s="6" t="s">
         <v>19</v>
@@ -47832,44 +47710,44 @@
       </c>
     </row>
     <row r="1060" ht="16" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1060" s="12" t="s">
+      <c r="A1060" s="2" t="s">
         <v>1151</v>
       </c>
-      <c r="B1060" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="C1060" s="12" t="s">
-        <v>240</v>
-      </c>
-      <c r="D1060" s="12" t="s">
-        <v>1259</v>
-      </c>
-      <c r="E1060" s="12" t="s">
+      <c r="B1060" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1060" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="D1060" s="2" t="s">
+        <v>1258</v>
+      </c>
+      <c r="E1060" s="2" t="s">
         <v>1153</v>
       </c>
-      <c r="F1060" s="12" t="s">
-        <v>36</v>
-      </c>
-      <c r="G1060" s="13">
+      <c r="F1060" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="G1060" s="3">
         <v>7</v>
       </c>
-      <c r="H1060" s="12" t="s">
+      <c r="H1060" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="I1060" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="J1060" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="K1060" s="15">
+      <c r="I1060" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1060" s="4">
+        <v>19800</v>
+      </c>
+      <c r="K1060" s="4">
         <v>16200</v>
       </c>
-      <c r="L1060" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="M1060" s="16" t="s">
-        <v>1165</v>
+      <c r="L1060" s="4">
+        <v>16200</v>
+      </c>
+      <c r="M1060" s="5" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="1061" ht="16" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -47883,7 +47761,7 @@
         <v>240</v>
       </c>
       <c r="D1061" s="6" t="s">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="E1061" s="6" t="s">
         <v>1153</v>
@@ -47895,7 +47773,7 @@
         <v>8</v>
       </c>
       <c r="H1061" s="6" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="I1061" s="6" t="s">
         <v>19</v>
@@ -47924,10 +47802,10 @@
         <v>240</v>
       </c>
       <c r="D1062" s="2" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="E1062" s="2" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="F1062" s="2" t="s">
         <v>79</v>
@@ -47965,7 +47843,7 @@
         <v>240</v>
       </c>
       <c r="D1063" s="6" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
       <c r="E1063" s="6" t="s">
         <v>1164</v>
@@ -48006,10 +47884,10 @@
         <v>240</v>
       </c>
       <c r="D1064" s="2" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="E1064" s="2" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="F1064" s="2" t="s">
         <v>109</v>
@@ -48047,7 +47925,7 @@
         <v>240</v>
       </c>
       <c r="D1065" s="6" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
       <c r="E1065" s="6" t="s">
         <v>1153</v>
@@ -48059,7 +47937,7 @@
         <v>2</v>
       </c>
       <c r="H1065" s="6" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="I1065" s="6" t="s">
         <v>19</v>
@@ -48088,7 +47966,7 @@
         <v>240</v>
       </c>
       <c r="D1066" s="2" t="s">
-        <v>1265</v>
+        <v>1264</v>
       </c>
       <c r="E1066" s="2" t="s">
         <v>1153</v>
@@ -48129,10 +48007,10 @@
         <v>240</v>
       </c>
       <c r="D1067" s="6" t="s">
+        <v>1265</v>
+      </c>
+      <c r="E1067" s="6" t="s">
         <v>1266</v>
-      </c>
-      <c r="E1067" s="6" t="s">
-        <v>1267</v>
       </c>
       <c r="F1067" s="6" t="s">
         <v>493</v>
@@ -48170,10 +48048,10 @@
         <v>240</v>
       </c>
       <c r="D1068" s="2" t="s">
+        <v>1267</v>
+      </c>
+      <c r="E1068" s="2" t="s">
         <v>1268</v>
-      </c>
-      <c r="E1068" s="2" t="s">
-        <v>1269</v>
       </c>
       <c r="F1068" s="2" t="s">
         <v>36</v>
@@ -48211,10 +48089,10 @@
         <v>240</v>
       </c>
       <c r="D1069" s="6" t="s">
+        <v>1269</v>
+      </c>
+      <c r="E1069" s="6" t="s">
         <v>1270</v>
-      </c>
-      <c r="E1069" s="6" t="s">
-        <v>1271</v>
       </c>
       <c r="F1069" s="6" t="s">
         <v>36</v>
@@ -48242,945 +48120,166 @@
       </c>
     </row>
     <row r="1070" ht="16" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1070" s="22" t="s">
+      <c r="A1070" s="2" t="s">
         <v>1151</v>
       </c>
-      <c r="B1070" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="C1070" s="22" t="s">
-        <v>240</v>
-      </c>
-      <c r="D1070" s="22" t="s">
+      <c r="B1070" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1070" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="D1070" s="2" t="s">
+        <v>1271</v>
+      </c>
+      <c r="E1070" s="2" t="s">
+        <v>1153</v>
+      </c>
+      <c r="F1070" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="G1070" s="3">
+        <v>2</v>
+      </c>
+      <c r="H1070" s="2" t="s">
+        <v>1184</v>
+      </c>
+      <c r="I1070" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1070" s="4">
+        <v>15400</v>
+      </c>
+      <c r="K1070" s="4">
+        <v>11100</v>
+      </c>
+      <c r="L1070" s="4">
+        <v>11100</v>
+      </c>
+      <c r="M1070" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1071" ht="16" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1071" s="6" t="s">
+        <v>1151</v>
+      </c>
+      <c r="B1071" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1071" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="D1071" s="6" t="s">
         <v>1272</v>
       </c>
-      <c r="E1070" s="22" t="s">
-        <v>36</v>
-      </c>
-      <c r="F1070" s="22" t="s">
-        <v>36</v>
-      </c>
-      <c r="G1070" s="22" t="s">
-        <v>19</v>
-      </c>
-      <c r="H1070" s="22" t="s">
-        <v>19</v>
-      </c>
-      <c r="I1070" s="22" t="s">
-        <v>19</v>
-      </c>
-      <c r="J1070" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="K1070" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="L1070" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="M1070" s="24" t="s">
+      <c r="E1071" s="6" t="s">
+        <v>1153</v>
+      </c>
+      <c r="F1071" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="G1071" s="7">
+        <v>4</v>
+      </c>
+      <c r="H1071" s="6" t="s">
+        <v>1184</v>
+      </c>
+      <c r="I1071" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1071" s="8">
+        <v>17600</v>
+      </c>
+      <c r="K1071" s="8">
+        <v>13100</v>
+      </c>
+      <c r="L1071" s="8">
+        <v>13100</v>
+      </c>
+      <c r="M1071" s="9" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1072" ht="16" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1072" s="2" t="s">
+        <v>1151</v>
+      </c>
+      <c r="B1072" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1072" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="D1072" s="2" t="s">
         <v>1273</v>
       </c>
-    </row>
-    <row r="1071" ht="16" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1071" s="22" t="s">
+      <c r="E1072" s="2" t="s">
+        <v>1153</v>
+      </c>
+      <c r="F1072" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="G1072" s="3">
+        <v>2</v>
+      </c>
+      <c r="H1072" s="2" t="s">
+        <v>1184</v>
+      </c>
+      <c r="I1072" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1072" s="4">
+        <v>14300</v>
+      </c>
+      <c r="K1072" s="4">
+        <v>9600</v>
+      </c>
+      <c r="L1072" s="4">
+        <v>9600</v>
+      </c>
+      <c r="M1072" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1073" ht="16" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1073" s="6" t="s">
         <v>1151</v>
       </c>
-      <c r="B1071" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="C1071" s="22" t="s">
-        <v>240</v>
-      </c>
-      <c r="D1071" s="22" t="s">
+      <c r="B1073" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1073" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="D1073" s="6" t="s">
         <v>1274</v>
       </c>
-      <c r="E1071" s="22" t="s">
-        <v>36</v>
-      </c>
-      <c r="F1071" s="22" t="s">
-        <v>36</v>
-      </c>
-      <c r="G1071" s="22" t="s">
-        <v>19</v>
-      </c>
-      <c r="H1071" s="22" t="s">
-        <v>19</v>
-      </c>
-      <c r="I1071" s="22" t="s">
-        <v>19</v>
-      </c>
-      <c r="J1071" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="K1071" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="L1071" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="M1071" s="24" t="s">
-        <v>1273</v>
-      </c>
-    </row>
-    <row r="1072" ht="16" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1072" s="22" t="s">
-        <v>1151</v>
-      </c>
-      <c r="B1072" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="C1072" s="22" t="s">
-        <v>240</v>
-      </c>
-      <c r="D1072" s="22" t="s">
-        <v>1275</v>
-      </c>
-      <c r="E1072" s="22" t="s">
-        <v>36</v>
-      </c>
-      <c r="F1072" s="22" t="s">
-        <v>36</v>
-      </c>
-      <c r="G1072" s="22" t="s">
-        <v>19</v>
-      </c>
-      <c r="H1072" s="22" t="s">
-        <v>19</v>
-      </c>
-      <c r="I1072" s="22" t="s">
-        <v>19</v>
-      </c>
-      <c r="J1072" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="K1072" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="L1072" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="M1072" s="24" t="s">
-        <v>1273</v>
-      </c>
-    </row>
-    <row r="1073" ht="16" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1073" s="22" t="s">
-        <v>1151</v>
-      </c>
-      <c r="B1073" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="C1073" s="22" t="s">
-        <v>240</v>
-      </c>
-      <c r="D1073" s="22" t="s">
-        <v>1276</v>
-      </c>
-      <c r="E1073" s="22" t="s">
-        <v>36</v>
-      </c>
-      <c r="F1073" s="22" t="s">
-        <v>36</v>
-      </c>
-      <c r="G1073" s="22" t="s">
-        <v>19</v>
-      </c>
-      <c r="H1073" s="22" t="s">
-        <v>19</v>
-      </c>
-      <c r="I1073" s="22" t="s">
-        <v>19</v>
-      </c>
-      <c r="J1073" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="K1073" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="L1073" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="M1073" s="24" t="s">
-        <v>1273</v>
-      </c>
-    </row>
-    <row r="1074" ht="16" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1074" s="22" t="s">
-        <v>1151</v>
-      </c>
-      <c r="B1074" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="C1074" s="22" t="s">
-        <v>240</v>
-      </c>
-      <c r="D1074" s="22" t="s">
-        <v>1277</v>
-      </c>
-      <c r="E1074" s="22" t="s">
-        <v>36</v>
-      </c>
-      <c r="F1074" s="22" t="s">
-        <v>36</v>
-      </c>
-      <c r="G1074" s="22" t="s">
-        <v>19</v>
-      </c>
-      <c r="H1074" s="22" t="s">
-        <v>19</v>
-      </c>
-      <c r="I1074" s="22" t="s">
-        <v>19</v>
-      </c>
-      <c r="J1074" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="K1074" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="L1074" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="M1074" s="24" t="s">
-        <v>1273</v>
-      </c>
-    </row>
-    <row r="1075" ht="16" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1075" s="22" t="s">
-        <v>1151</v>
-      </c>
-      <c r="B1075" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="C1075" s="22" t="s">
-        <v>240</v>
-      </c>
-      <c r="D1075" s="22" t="s">
-        <v>1278</v>
-      </c>
-      <c r="E1075" s="22" t="s">
-        <v>36</v>
-      </c>
-      <c r="F1075" s="22" t="s">
-        <v>36</v>
-      </c>
-      <c r="G1075" s="22" t="s">
-        <v>19</v>
-      </c>
-      <c r="H1075" s="22" t="s">
-        <v>19</v>
-      </c>
-      <c r="I1075" s="22" t="s">
-        <v>19</v>
-      </c>
-      <c r="J1075" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="K1075" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="L1075" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="M1075" s="24" t="s">
-        <v>1273</v>
-      </c>
-    </row>
-    <row r="1076" ht="16" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1076" s="22" t="s">
-        <v>1151</v>
-      </c>
-      <c r="B1076" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="C1076" s="22" t="s">
-        <v>240</v>
-      </c>
-      <c r="D1076" s="22" t="s">
-        <v>1279</v>
-      </c>
-      <c r="E1076" s="22" t="s">
-        <v>36</v>
-      </c>
-      <c r="F1076" s="22" t="s">
-        <v>36</v>
-      </c>
-      <c r="G1076" s="22" t="s">
-        <v>19</v>
-      </c>
-      <c r="H1076" s="22" t="s">
-        <v>19</v>
-      </c>
-      <c r="I1076" s="22" t="s">
-        <v>19</v>
-      </c>
-      <c r="J1076" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="K1076" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="L1076" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="M1076" s="24" t="s">
-        <v>1273</v>
-      </c>
-    </row>
-    <row r="1077" ht="16" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1077" s="22" t="s">
-        <v>1151</v>
-      </c>
-      <c r="B1077" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="C1077" s="22" t="s">
-        <v>240</v>
-      </c>
-      <c r="D1077" s="22" t="s">
-        <v>1280</v>
-      </c>
-      <c r="E1077" s="22" t="s">
-        <v>36</v>
-      </c>
-      <c r="F1077" s="22" t="s">
-        <v>36</v>
-      </c>
-      <c r="G1077" s="22" t="s">
-        <v>19</v>
-      </c>
-      <c r="H1077" s="22" t="s">
-        <v>19</v>
-      </c>
-      <c r="I1077" s="22" t="s">
-        <v>19</v>
-      </c>
-      <c r="J1077" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="K1077" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="L1077" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="M1077" s="24" t="s">
-        <v>1273</v>
-      </c>
-    </row>
-    <row r="1078" ht="16" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1078" s="22" t="s">
-        <v>1151</v>
-      </c>
-      <c r="B1078" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="C1078" s="22" t="s">
-        <v>240</v>
-      </c>
-      <c r="D1078" s="22" t="s">
-        <v>1281</v>
-      </c>
-      <c r="E1078" s="22" t="s">
-        <v>36</v>
-      </c>
-      <c r="F1078" s="22" t="s">
-        <v>36</v>
-      </c>
-      <c r="G1078" s="22" t="s">
-        <v>19</v>
-      </c>
-      <c r="H1078" s="22" t="s">
-        <v>19</v>
-      </c>
-      <c r="I1078" s="22" t="s">
-        <v>19</v>
-      </c>
-      <c r="J1078" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="K1078" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="L1078" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="M1078" s="24" t="s">
-        <v>1273</v>
-      </c>
-    </row>
-    <row r="1079" ht="16" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1079" s="22" t="s">
-        <v>1151</v>
-      </c>
-      <c r="B1079" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="C1079" s="22" t="s">
-        <v>240</v>
-      </c>
-      <c r="D1079" s="22" t="s">
-        <v>1282</v>
-      </c>
-      <c r="E1079" s="22" t="s">
-        <v>36</v>
-      </c>
-      <c r="F1079" s="22" t="s">
-        <v>36</v>
-      </c>
-      <c r="G1079" s="22" t="s">
-        <v>19</v>
-      </c>
-      <c r="H1079" s="22" t="s">
-        <v>19</v>
-      </c>
-      <c r="I1079" s="22" t="s">
-        <v>19</v>
-      </c>
-      <c r="J1079" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="K1079" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="L1079" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="M1079" s="24" t="s">
-        <v>1273</v>
-      </c>
-    </row>
-    <row r="1080" ht="16" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1080" s="22" t="s">
-        <v>1151</v>
-      </c>
-      <c r="B1080" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="C1080" s="22" t="s">
-        <v>240</v>
-      </c>
-      <c r="D1080" s="22" t="s">
-        <v>1283</v>
-      </c>
-      <c r="E1080" s="22" t="s">
-        <v>36</v>
-      </c>
-      <c r="F1080" s="22" t="s">
-        <v>36</v>
-      </c>
-      <c r="G1080" s="22" t="s">
-        <v>19</v>
-      </c>
-      <c r="H1080" s="22" t="s">
-        <v>19</v>
-      </c>
-      <c r="I1080" s="22" t="s">
-        <v>19</v>
-      </c>
-      <c r="J1080" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="K1080" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="L1080" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="M1080" s="24" t="s">
-        <v>1273</v>
-      </c>
-    </row>
-    <row r="1081" ht="16" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1081" s="22" t="s">
-        <v>1151</v>
-      </c>
-      <c r="B1081" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="C1081" s="22" t="s">
-        <v>240</v>
-      </c>
-      <c r="D1081" s="22" t="s">
-        <v>1284</v>
-      </c>
-      <c r="E1081" s="22" t="s">
-        <v>36</v>
-      </c>
-      <c r="F1081" s="22" t="s">
-        <v>36</v>
-      </c>
-      <c r="G1081" s="22" t="s">
-        <v>19</v>
-      </c>
-      <c r="H1081" s="22" t="s">
-        <v>19</v>
-      </c>
-      <c r="I1081" s="22" t="s">
-        <v>19</v>
-      </c>
-      <c r="J1081" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="K1081" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="L1081" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="M1081" s="24" t="s">
-        <v>1273</v>
-      </c>
-    </row>
-    <row r="1082" ht="16" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1082" s="22" t="s">
-        <v>1151</v>
-      </c>
-      <c r="B1082" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="C1082" s="22" t="s">
-        <v>240</v>
-      </c>
-      <c r="D1082" s="22" t="s">
-        <v>1285</v>
-      </c>
-      <c r="E1082" s="22" t="s">
-        <v>36</v>
-      </c>
-      <c r="F1082" s="22" t="s">
-        <v>36</v>
-      </c>
-      <c r="G1082" s="22" t="s">
-        <v>19</v>
-      </c>
-      <c r="H1082" s="22" t="s">
-        <v>19</v>
-      </c>
-      <c r="I1082" s="22" t="s">
-        <v>19</v>
-      </c>
-      <c r="J1082" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="K1082" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="L1082" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="M1082" s="24" t="s">
-        <v>1273</v>
-      </c>
-    </row>
-    <row r="1083" ht="16" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1083" s="22" t="s">
-        <v>1151</v>
-      </c>
-      <c r="B1083" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="C1083" s="22" t="s">
-        <v>240</v>
-      </c>
-      <c r="D1083" s="22" t="s">
-        <v>1286</v>
-      </c>
-      <c r="E1083" s="22" t="s">
-        <v>36</v>
-      </c>
-      <c r="F1083" s="22" t="s">
-        <v>36</v>
-      </c>
-      <c r="G1083" s="22" t="s">
-        <v>19</v>
-      </c>
-      <c r="H1083" s="22" t="s">
-        <v>19</v>
-      </c>
-      <c r="I1083" s="22" t="s">
-        <v>19</v>
-      </c>
-      <c r="J1083" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="K1083" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="L1083" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="M1083" s="24" t="s">
-        <v>1273</v>
-      </c>
-    </row>
-    <row r="1084" ht="16" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1084" s="22" t="s">
-        <v>1151</v>
-      </c>
-      <c r="B1084" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="C1084" s="22" t="s">
-        <v>240</v>
-      </c>
-      <c r="D1084" s="22" t="s">
-        <v>1287</v>
-      </c>
-      <c r="E1084" s="22" t="s">
-        <v>36</v>
-      </c>
-      <c r="F1084" s="22" t="s">
-        <v>36</v>
-      </c>
-      <c r="G1084" s="22" t="s">
-        <v>19</v>
-      </c>
-      <c r="H1084" s="22" t="s">
-        <v>19</v>
-      </c>
-      <c r="I1084" s="22" t="s">
-        <v>19</v>
-      </c>
-      <c r="J1084" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="K1084" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="L1084" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="M1084" s="24" t="s">
-        <v>1273</v>
-      </c>
-    </row>
-    <row r="1085" ht="16" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1085" s="22" t="s">
-        <v>1151</v>
-      </c>
-      <c r="B1085" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="C1085" s="22" t="s">
-        <v>240</v>
-      </c>
-      <c r="D1085" s="22" t="s">
-        <v>1288</v>
-      </c>
-      <c r="E1085" s="22" t="s">
-        <v>36</v>
-      </c>
-      <c r="F1085" s="22" t="s">
-        <v>36</v>
-      </c>
-      <c r="G1085" s="22" t="s">
-        <v>19</v>
-      </c>
-      <c r="H1085" s="22" t="s">
-        <v>19</v>
-      </c>
-      <c r="I1085" s="22" t="s">
-        <v>19</v>
-      </c>
-      <c r="J1085" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="K1085" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="L1085" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="M1085" s="24" t="s">
-        <v>1273</v>
-      </c>
-    </row>
-    <row r="1086" ht="16" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1086" s="22" t="s">
-        <v>1151</v>
-      </c>
-      <c r="B1086" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="C1086" s="22" t="s">
-        <v>240</v>
-      </c>
-      <c r="D1086" s="22" t="s">
-        <v>1289</v>
-      </c>
-      <c r="E1086" s="22" t="s">
-        <v>36</v>
-      </c>
-      <c r="F1086" s="22" t="s">
-        <v>36</v>
-      </c>
-      <c r="G1086" s="22" t="s">
-        <v>19</v>
-      </c>
-      <c r="H1086" s="22" t="s">
-        <v>19</v>
-      </c>
-      <c r="I1086" s="22" t="s">
-        <v>19</v>
-      </c>
-      <c r="J1086" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="K1086" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="L1086" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="M1086" s="24" t="s">
-        <v>1273</v>
-      </c>
-    </row>
-    <row r="1087" ht="16" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1087" s="22" t="s">
-        <v>1151</v>
-      </c>
-      <c r="B1087" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="C1087" s="22" t="s">
-        <v>240</v>
-      </c>
-      <c r="D1087" s="22" t="s">
-        <v>1290</v>
-      </c>
-      <c r="E1087" s="22" t="s">
-        <v>36</v>
-      </c>
-      <c r="F1087" s="22" t="s">
-        <v>36</v>
-      </c>
-      <c r="G1087" s="22" t="s">
-        <v>19</v>
-      </c>
-      <c r="H1087" s="22" t="s">
-        <v>19</v>
-      </c>
-      <c r="I1087" s="22" t="s">
-        <v>19</v>
-      </c>
-      <c r="J1087" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="K1087" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="L1087" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="M1087" s="24" t="s">
-        <v>1273</v>
-      </c>
-    </row>
-    <row r="1088" ht="16" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1088" s="22" t="s">
-        <v>1151</v>
-      </c>
-      <c r="B1088" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="C1088" s="22" t="s">
-        <v>240</v>
-      </c>
-      <c r="D1088" s="22" t="s">
-        <v>1291</v>
-      </c>
-      <c r="E1088" s="22" t="s">
-        <v>36</v>
-      </c>
-      <c r="F1088" s="22" t="s">
-        <v>36</v>
-      </c>
-      <c r="G1088" s="22" t="s">
-        <v>19</v>
-      </c>
-      <c r="H1088" s="22" t="s">
-        <v>19</v>
-      </c>
-      <c r="I1088" s="22" t="s">
-        <v>19</v>
-      </c>
-      <c r="J1088" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="K1088" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="L1088" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="M1088" s="24" t="s">
-        <v>1273</v>
-      </c>
-    </row>
-    <row r="1089" ht="16" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1089" s="17" t="s">
-        <v>1151</v>
-      </c>
-      <c r="B1089" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="C1089" s="17" t="s">
-        <v>240</v>
-      </c>
-      <c r="D1089" s="17" t="s">
-        <v>1292</v>
-      </c>
-      <c r="E1089" s="17" t="s">
+      <c r="E1073" s="6" t="s">
         <v>1153</v>
       </c>
-      <c r="F1089" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="G1089" s="18">
-        <v>2</v>
-      </c>
-      <c r="H1089" s="17" t="s">
-        <v>1185</v>
-      </c>
-      <c r="I1089" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="J1089" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="K1089" s="20">
-        <v>11100</v>
-      </c>
-      <c r="L1089" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="M1089" s="21" t="s">
-        <v>1165</v>
-      </c>
-    </row>
-    <row r="1090" ht="16" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1090" s="2" t="s">
-        <v>1151</v>
-      </c>
-      <c r="B1090" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C1090" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="D1090" s="2" t="s">
-        <v>1293</v>
-      </c>
-      <c r="E1090" s="2" t="s">
-        <v>1153</v>
-      </c>
-      <c r="F1090" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="G1090" s="3">
+      <c r="F1073" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="G1073" s="7">
         <v>4</v>
       </c>
-      <c r="H1090" s="2" t="s">
-        <v>1185</v>
-      </c>
-      <c r="I1090" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="J1090" s="4">
-        <v>17600</v>
-      </c>
-      <c r="K1090" s="4">
-        <v>13100</v>
-      </c>
-      <c r="L1090" s="4">
-        <v>13100</v>
-      </c>
-      <c r="M1090" s="5" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="1091" ht="16" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1091" s="6" t="s">
-        <v>1151</v>
-      </c>
-      <c r="B1091" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C1091" s="6" t="s">
-        <v>240</v>
-      </c>
-      <c r="D1091" s="6" t="s">
-        <v>1294</v>
-      </c>
-      <c r="E1091" s="6" t="s">
-        <v>1153</v>
-      </c>
-      <c r="F1091" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="G1091" s="7">
-        <v>2</v>
-      </c>
-      <c r="H1091" s="6" t="s">
-        <v>1185</v>
-      </c>
-      <c r="I1091" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="J1091" s="8">
-        <v>14300</v>
-      </c>
-      <c r="K1091" s="8">
-        <v>9600</v>
-      </c>
-      <c r="L1091" s="8">
-        <v>9600</v>
-      </c>
-      <c r="M1091" s="9" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="1092" ht="16" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1092" s="2" t="s">
-        <v>1151</v>
-      </c>
-      <c r="B1092" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C1092" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="D1092" s="2" t="s">
-        <v>1295</v>
-      </c>
-      <c r="E1092" s="2" t="s">
-        <v>1153</v>
-      </c>
-      <c r="F1092" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="G1092" s="3">
-        <v>4</v>
-      </c>
-      <c r="H1092" s="2" t="s">
+      <c r="H1073" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="I1092" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="J1092" s="4">
+      <c r="I1073" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1073" s="8">
         <v>16500</v>
       </c>
-      <c r="K1092" s="4">
+      <c r="K1073" s="8">
         <v>12100</v>
       </c>
-      <c r="L1092" s="4">
+      <c r="L1073" s="8">
         <v>12100</v>
       </c>
-      <c r="M1092" s="5" t="s">
+      <c r="M1073" s="9" t="s">
         <v>20</v>
       </c>
     </row>
